--- a/media/Levels/Level_11ver2.0.xlsx
+++ b/media/Levels/Level_11ver2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\2024年３月特別授業\BaseCross64\DoctorRemote\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DF83CC4-403F-4B4F-AE6F-9B3218C5D537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A27630-27FF-49C8-B800-5A6A951D2102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -667,10 +667,10 @@
         <v>0</v>
       </c>
       <c r="BW1" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BX1" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BY1" s="1">
         <v>0</v>
@@ -14333,10 +14333,10 @@
         <v>0</v>
       </c>
       <c r="BW150" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BX150" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BY150" s="1">
         <v>0</v>
